--- a/artfynd/A 36502-2025 artfynd.xlsx
+++ b/artfynd/A 36502-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128120144</v>
       </c>
       <c r="B2" t="n">
-        <v>92668</v>
+        <v>92669</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36502-2025 artfynd.xlsx
+++ b/artfynd/A 36502-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128120144</v>
       </c>
       <c r="B2" t="n">
-        <v>92669</v>
+        <v>92670</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36502-2025 artfynd.xlsx
+++ b/artfynd/A 36502-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128120144</v>
       </c>
       <c r="B2" t="n">
-        <v>92670</v>
+        <v>92678</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36502-2025 artfynd.xlsx
+++ b/artfynd/A 36502-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128120144</v>
       </c>
       <c r="B2" t="n">
-        <v>92678</v>
+        <v>92770</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>128120060</v>
       </c>
       <c r="B3" t="n">
-        <v>56864</v>
+        <v>56876</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>128120212</v>
       </c>
       <c r="B4" t="n">
-        <v>56864</v>
+        <v>56876</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 36502-2025 artfynd.xlsx
+++ b/artfynd/A 36502-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128120144</v>
       </c>
       <c r="B2" t="n">
-        <v>92770</v>
+        <v>92782</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>128120060</v>
       </c>
       <c r="B3" t="n">
-        <v>56876</v>
+        <v>56880</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>128120212</v>
       </c>
       <c r="B4" t="n">
-        <v>56876</v>
+        <v>56880</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 36502-2025 artfynd.xlsx
+++ b/artfynd/A 36502-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128120144</v>
       </c>
       <c r="B2" t="n">
-        <v>92782</v>
+        <v>92784</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36502-2025 artfynd.xlsx
+++ b/artfynd/A 36502-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128120144</v>
       </c>
       <c r="B2" t="n">
-        <v>92784</v>
+        <v>92785</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36502-2025 artfynd.xlsx
+++ b/artfynd/A 36502-2025 artfynd.xlsx
@@ -771,7 +771,7 @@
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>

--- a/artfynd/A 36502-2025 artfynd.xlsx
+++ b/artfynd/A 36502-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,42 +675,47 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128120144</v>
+        <v>128120060</v>
       </c>
       <c r="B2" t="n">
-        <v>92785</v>
+        <v>57141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5449</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -722,7 +727,7 @@
         <v>632917</v>
       </c>
       <c r="R2" t="n">
-        <v>6557795</v>
+        <v>6557799</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -771,7 +776,7 @@
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
@@ -791,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128120060</v>
+        <v>128120212</v>
       </c>
       <c r="B3" t="n">
-        <v>56880</v>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,17 +826,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>stationär</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>632917</v>
+        <v>632829</v>
       </c>
       <c r="R3" t="n">
-        <v>6557799</v>
+        <v>6557823</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,7 +875,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,122 +909,6 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>128120212</v>
-      </c>
-      <c r="B4" t="n">
-        <v>56880</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>100138</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Tetrao urogallus</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Ropudden, Ropudden, Srm</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>632829</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6557823</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Stockholm</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Södertälje</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Vårdinge</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2025-09-01</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>09:06</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2025-09-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>09:06</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Gustaf Eibl</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Gustaf Eibl</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36502-2025 artfynd.xlsx
+++ b/artfynd/A 36502-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128120060</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -909,8 +919,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128120212</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>